--- a/Data/g1.9.xlsx
+++ b/Data/g1.9.xlsx
@@ -448,15 +448,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+          <t>Atividades imobiliárias</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.3618246924122</v>
+        <v>28.31208085602502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2013 / 2022</t>
+          <t>2014 / 2023</t>
         </is>
       </c>
     </row>
@@ -467,26 +467,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.4933798284287</v>
+        <v>23.65397356444598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2013 / 2022</t>
+          <t>2014 / 2023</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atividades imobiliárias</t>
+          <t>Eletricidade e gás, água, esgoto, atividades de gestão de resíduos e descontaminação</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.40818553225802</v>
+        <v>22.70215620370851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2013 / 2022</t>
+          <t>2014 / 2023</t>
         </is>
       </c>
     </row>
@@ -497,56 +497,56 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.265557954021503</v>
+        <v>18.69747267971518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2013 / 2022</t>
+          <t>2014 / 2023</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Administração, defesa, educação e saúde públicas e seguridade social</t>
+          <t>Agropecuária</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.709036955545471</v>
+        <v>5.682545327113388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2013 / 2022</t>
+          <t>2014 / 2023</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agropecuária</t>
+          <t>Administração, defesa, educação e saúde públicas e seguridade social</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-4.003418719932625</v>
+        <v>2.548568009332001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2013 / 2022</t>
+          <t>2014 / 2023</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Transporte, armazenagem e correio</t>
+          <t>Indústrias extrativas</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.77773366884247</v>
+        <v>69.71390886407463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2021 / 2022</t>
+          <t>2022 / 2023</t>
         </is>
       </c>
     </row>
@@ -557,71 +557,71 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.521894003851491</v>
+        <v>7.64923808343667</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2021 / 2022</t>
+          <t>2022 / 2023</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Construção</t>
+          <t>Informação e comunicação</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.438360842135382</v>
+        <v>7.133426276710783</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2021 / 2022</t>
+          <t>2022 / 2023</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Informação e comunicação</t>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.037854550070413</v>
+        <v>4.80083445372183</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2021 / 2022</t>
+          <t>2022 / 2023</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Atividades imobiliárias</t>
+          <t>Comércio e reparação de veículos automotores e motocicletas</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.551068180916705</v>
+        <v>2.010492569309139</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2021 / 2022</t>
+          <t>2022 / 2023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Administração, defesa, educação e saúde públicas e seguridade social</t>
+          <t>Indústrias de transformação</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.274864519824148</v>
+        <v>1.925088415038929</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2021 / 2022</t>
+          <t>2022 / 2023</t>
         </is>
       </c>
     </row>
